--- a/extenbooks/S901_extenbook.xlsx
+++ b/extenbooks/S901_extenbook.xlsx
@@ -23779,7 +23779,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**DPR** · **Phase**: 5 · **Series ID**: S901 · **Status**: ingested · **Authored**: 2026-05-18</t>
+          <t>**DPR** · **Phase**: 5 · **Series ID**: S901 · **Status**: book_period_validated · **Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
@@ -25267,11 +25267,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25294,76 +25294,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Market Prices vs Direct Prices, 71 Industries</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S901_research.json", "adequacy_report": "Technical/docs/chapters/CH9_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S901_DPR.md", "epr": "Technical/docs/series/S901_EPR.md", "loader": "Technical/code/L01_loaders/L01_S901_load.py", "processor": "Technical/code/P02_processors/P02_S901_construct.py", "validator": "Technical/code/V03_validators/V03_S901_validate.py", "processed": "Technical/data/processed/S901.parquet", "chopped_csv": "Technical/chopped/S901.csv", "extenbook_xlsx": "Technical/extenbooks/S901_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T23:56:32.581279+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S901_extenbook.xlsx
+++ b/extenbooks/S901_extenbook.xlsx
@@ -25207,7 +25207,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-19T00:03:42.340776+00:00</t>
+          <t>2026-07-02T06:26:18.786823+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S901_extenbook.xlsx
+++ b/extenbooks/S901_extenbook.xlsx
@@ -25252,7 +25252,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-02T06:26:18.786823+00:00</t>
+          <t>2026-07-11T03:44:26.543531+00:00</t>
         </is>
       </c>
     </row>
@@ -25267,11 +25267,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25294,6 +25294,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_9_1998F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful reconstruction of the data behind Shaikh Figures 9.1, 9.2 and 9.16 (Ch9, Section V). For each US benchmark input-output table (1947, 1958, 1963, 1967, 1972 at 71-order; 1998 at 65-order, circulating and fixed-capital variants) it pairs each industry's normalized total market price (A) with its normalized total direct price (B), the test of Ricardo's cross-sectional hypothesis that the two are close. Construction-relevant: the empirical core of Chapter 9 (market prices differ from direct prices by only ~15-18% across half a century). The year column indexes the benchmark cross-section; the genuine axis is the industry index. All subseries share one dimensionless unit (normalized share); no mixed units.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S901_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S901_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6 benchmark years; NAICS/SIC break prevents continuous panel. Fig 9.16 substrate (market prices) lives here, production-price overlay from S902. | P2.6 F-P2.1-07 (observation): the Table 9.9 CV / delta-e distance measures reproduce for 1947 but diverge in mid-years (e.g. 1958 CV .215 vs .179), consistent with Shaikh's depreciation / mu adjustments; these dispersion measures are outside the anchor vocabulary and are not a data defect. S901's live independent anchor (1998 log-log market~direct R2=0.973) remains GREEN. No change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>normalized_share</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
